--- a/templates/workbook.xlsx
+++ b/templates/workbook.xlsx
@@ -5,21 +5,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="land" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cost" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="noi_adj" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cap_rates" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pgi_calc" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lease_comps" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lease_metrics" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qualitative_analysis" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subject_units" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="expense_comp" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="outputs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_data" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dilmore" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sca_adjustment_grid" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cost" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="noi_adj" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cap_rates" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pgi_calc" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lease_comps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lease_metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qualitative_analysis" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subject_units" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="expense_comp" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="outputs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_data" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dilmore" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sca_adjustment_grid" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="land_adjustment_grid" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -562,7 +562,7 @@
     <xf numFmtId="9" fontId="18" fillId="0" borderId="8"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="8"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1220,6 +1220,11 @@
     <xf numFmtId="173" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0"/>
@@ -3821,365 +3826,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.19999980926514"/>
-  <cols>
-    <col width="2" customWidth="1" style="160" min="1" max="1"/>
-    <col width="22" customWidth="1" style="160" min="2" max="2"/>
-    <col width="40.6640625" customWidth="1" style="160" min="3" max="3"/>
-    <col width="12" customWidth="1" style="160" min="4" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="6" customHeight="1" s="160"/>
-    <row r="2" ht="18" customHeight="1" s="160">
-      <c r="B2" s="236" t="inlineStr">
-        <is>
-          <t>LEASE COMPARABLE — QUALITATIVE ANALYSIS</t>
-        </is>
-      </c>
-      <c r="C2" s="162" t="n"/>
-      <c r="D2" s="162" t="n"/>
-      <c r="E2" s="162" t="n"/>
-      <c r="F2" s="162" t="n"/>
-      <c r="G2" s="162" t="n"/>
-      <c r="H2" s="162" t="n"/>
-      <c r="I2" s="162" t="n"/>
-      <c r="J2" s="163" t="n"/>
-    </row>
-    <row r="3" ht="13.94999980926514" customHeight="1" s="160">
-      <c r="B3" s="239" t="n"/>
-      <c r="C3" s="162" t="n"/>
-      <c r="D3" s="162" t="n"/>
-      <c r="E3" s="162" t="n"/>
-      <c r="F3" s="162" t="n"/>
-      <c r="G3" s="162" t="n"/>
-      <c r="H3" s="162" t="n"/>
-      <c r="I3" s="162" t="n"/>
-      <c r="J3" s="163" t="n"/>
-    </row>
-    <row r="4" ht="16.04999923706055" customHeight="1" s="160">
-      <c r="B4" s="37" t="inlineStr">
-        <is>
-          <t>Comp No.</t>
-        </is>
-      </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="inlineStr">
-        <is>
-          <t>Rate ($/SF)</t>
-        </is>
-      </c>
-      <c r="E4" s="37" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="F4" s="37" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="G4" s="37" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="H4" s="37" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="I4" s="37" t="inlineStr">
-        <is>
-          <t>Lease Terms</t>
-        </is>
-      </c>
-      <c r="J4" s="37" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="160">
-      <c r="B5" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="56" t="n"/>
-      <c r="D5" s="75" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
-      <c r="I5" s="41" t="n"/>
-      <c r="J5" s="41" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="160">
-      <c r="B6" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="58" t="n"/>
-      <c r="D6" s="78" t="n"/>
-      <c r="E6" s="44" t="n"/>
-      <c r="F6" s="44" t="n"/>
-      <c r="G6" s="44" t="n"/>
-      <c r="H6" s="99" t="n"/>
-      <c r="I6" s="100" t="n"/>
-      <c r="J6" s="44" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="160">
-      <c r="B7" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="56" t="n"/>
-      <c r="D7" s="75" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
-      <c r="I7" s="41" t="n"/>
-      <c r="J7" s="41" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="160">
-      <c r="B8" s="58" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="58" t="n"/>
-      <c r="D8" s="78" t="n"/>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="44" t="n"/>
-      <c r="G8" s="44" t="n"/>
-      <c r="H8" s="99" t="n"/>
-      <c r="I8" s="100" t="n"/>
-      <c r="J8" s="44" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="160">
-      <c r="B9" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="56" t="n"/>
-      <c r="D9" s="75" t="n"/>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="41" t="n"/>
-      <c r="H9" s="41" t="n"/>
-      <c r="I9" s="41" t="n"/>
-      <c r="J9" s="99" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="160">
-      <c r="B10" s="58" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="58" t="n"/>
-      <c r="D10" s="78" t="n"/>
-      <c r="E10" s="99" t="n"/>
-      <c r="F10" s="99" t="n"/>
-      <c r="G10" s="44" t="n"/>
-      <c r="H10" s="99" t="n"/>
-      <c r="I10" s="100" t="n"/>
-      <c r="J10" s="99" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="160">
-      <c r="B11" s="56" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="56" t="n"/>
-      <c r="D11" s="75" t="n"/>
-      <c r="E11" s="100" t="n"/>
-      <c r="F11" s="41" t="n"/>
-      <c r="G11" s="41" t="n"/>
-      <c r="H11" s="41" t="n"/>
-      <c r="I11" s="41" t="n"/>
-      <c r="J11" s="100" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="160">
-      <c r="B12" s="58" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="58" t="n"/>
-      <c r="D12" s="78" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="99" t="n"/>
-      <c r="G12" s="99" t="n"/>
-      <c r="H12" s="100" t="n"/>
-      <c r="I12" s="44" t="n"/>
-      <c r="J12" s="99" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="160">
-      <c r="B13" s="56" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="56" t="n"/>
-      <c r="D13" s="75" t="n"/>
-      <c r="E13" s="41" t="n"/>
-      <c r="F13" s="41" t="n"/>
-      <c r="G13" s="41" t="n"/>
-      <c r="H13" s="99" t="n"/>
-      <c r="I13" s="41" t="n"/>
-      <c r="J13" s="99" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="160">
-      <c r="B14" s="58" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="58" t="n"/>
-      <c r="D14" s="78" t="n"/>
-      <c r="E14" s="99" t="n"/>
-      <c r="F14" s="99" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="100" t="n"/>
-      <c r="I14" s="100" t="n"/>
-      <c r="J14" s="99" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="160">
-      <c r="B15" s="56" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="56" t="n"/>
-      <c r="D15" s="75" t="n"/>
-      <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
-      <c r="G15" s="41" t="n"/>
-      <c r="H15" s="99" t="n"/>
-      <c r="I15" s="100" t="n"/>
-      <c r="J15" s="41" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="160">
-      <c r="B16" s="58" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="58" t="n"/>
-      <c r="D16" s="78" t="n"/>
-      <c r="E16" s="100" t="n"/>
-      <c r="F16" s="44" t="n"/>
-      <c r="G16" s="44" t="n"/>
-      <c r="H16" s="99" t="n"/>
-      <c r="I16" s="100" t="n"/>
-      <c r="J16" s="100" t="n"/>
-    </row>
-    <row r="17" ht="6" customHeight="1" s="160"/>
-    <row r="18" ht="18" customHeight="1" s="160">
-      <c r="B18" s="236" t="inlineStr">
-        <is>
-          <t>MARKET RENT CONCLUSION</t>
-        </is>
-      </c>
-      <c r="C18" s="162" t="n"/>
-      <c r="D18" s="162" t="n"/>
-      <c r="E18" s="162" t="n"/>
-      <c r="F18" s="162" t="n"/>
-      <c r="G18" s="162" t="n"/>
-      <c r="H18" s="162" t="n"/>
-      <c r="I18" s="162" t="n"/>
-      <c r="J18" s="163" t="n"/>
-    </row>
-    <row r="19" ht="28.20000076293945" customHeight="1" s="160">
-      <c r="B19" s="56" t="inlineStr">
-        <is>
-          <t>Range of Comparable Rates:</t>
-        </is>
-      </c>
-      <c r="C19" s="56" t="n"/>
-      <c r="D19" s="56" t="n"/>
-      <c r="E19" s="56" t="n"/>
-      <c r="F19" s="56" t="n"/>
-      <c r="G19" s="56" t="n"/>
-      <c r="H19" s="56" t="n"/>
-      <c r="I19" s="56" t="n"/>
-      <c r="J19" s="56" t="n"/>
-    </row>
-    <row r="20" ht="35.40000152587891" customHeight="1" s="160">
-      <c r="B20" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Most Comparable Comps </t>
-        </is>
-      </c>
-      <c r="C20" s="58" t="n"/>
-      <c r="D20" s="58" t="n"/>
-      <c r="E20" s="58" t="n"/>
-      <c r="F20" s="58" t="n"/>
-      <c r="G20" s="58" t="n"/>
-      <c r="H20" s="58" t="n"/>
-      <c r="I20" s="58" t="n"/>
-      <c r="J20" s="58" t="n"/>
-    </row>
-    <row r="21" ht="35.40000152587891" customHeight="1" s="160">
-      <c r="B21" s="58" t="inlineStr">
-        <is>
-          <t>Size Adjustment:</t>
-        </is>
-      </c>
-      <c r="C21" s="58" t="n"/>
-      <c r="D21" s="58" t="n"/>
-      <c r="E21" s="58" t="n"/>
-      <c r="F21" s="58" t="n"/>
-      <c r="G21" s="58" t="n"/>
-      <c r="H21" s="58" t="n"/>
-      <c r="I21" s="58" t="n"/>
-      <c r="J21" s="58" t="n"/>
-    </row>
-    <row r="22" ht="37.20000076293945" customHeight="1" s="160">
-      <c r="B22" s="56" t="inlineStr">
-        <is>
-          <t>Concluded Market Rent:</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="n"/>
-      <c r="D22" s="56" t="n"/>
-      <c r="E22" s="56" t="n"/>
-      <c r="F22" s="56" t="n"/>
-      <c r="G22" s="56" t="n"/>
-      <c r="H22" s="56" t="n"/>
-      <c r="I22" s="56" t="n"/>
-      <c r="J22" s="56" t="n"/>
-    </row>
-    <row r="23" ht="6" customHeight="1" s="160"/>
-    <row r="24" ht="13.94999980926514" customHeight="1" s="160">
-      <c r="B24" s="62" t="inlineStr">
-        <is>
-          <t>Color Key:</t>
-        </is>
-      </c>
-      <c r="C24" s="62" t="inlineStr">
-        <is>
-          <t>Superior</t>
-        </is>
-      </c>
-      <c r="D24" s="62" t="inlineStr">
-        <is>
-          <t>Similar</t>
-        </is>
-      </c>
-      <c r="E24" s="62" t="inlineStr">
-        <is>
-          <t>Inferior</t>
-        </is>
-      </c>
-      <c r="F24" s="62" t="n"/>
-      <c r="G24" s="62" t="n"/>
-      <c r="H24" s="62" t="n"/>
-      <c r="I24" s="62" t="n"/>
-      <c r="J24" s="62" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B2:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.19999980926514"/>
   <cols>
@@ -4387,7 +4033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4714,7 +4360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5010,7 +4656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7410,7 +7056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8073,7 +7719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10958,7 +10604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11625,6 +11271,646 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="160" min="1" max="1"/>
+    <col width="22" customWidth="1" style="160" min="2" max="2"/>
+    <col width="13" customWidth="1" style="160" min="3" max="3"/>
+    <col width="13" customWidth="1" style="160" min="4" max="4"/>
+    <col width="13" customWidth="1" style="160" min="5" max="5"/>
+    <col width="11" customWidth="1" style="160" min="6" max="6"/>
+    <col width="11" customWidth="1" style="160" min="7" max="7"/>
+    <col width="11" customWidth="1" style="160" min="8" max="8"/>
+    <col width="10" customWidth="1" style="160" min="9" max="9"/>
+    <col width="14" customWidth="1" style="160" min="10" max="10"/>
+    <col width="11" customWidth="1" style="160" min="11" max="11"/>
+    <col width="12" customWidth="1" style="160" min="12" max="12"/>
+    <col width="16" customWidth="1" style="160" min="13" max="13"/>
+    <col width="12" customWidth="1" style="160" min="14" max="14"/>
+    <col width="14" customWidth="1" style="160" min="15" max="15"/>
+    <col width="11" customWidth="1" style="160" min="16" max="16"/>
+    <col width="11" customWidth="1" style="160" min="17" max="17"/>
+    <col width="20" customWidth="1" style="160" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Land Sales Adjustment Grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="241" t="inlineStr">
+        <is>
+          <t>Subject: 100 Example Commerce Way, Sample City — 55,452 SF (1.27 Ac), Zone X, C-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="242" t="inlineStr">
+        <is>
+          <t>Comp</t>
+        </is>
+      </c>
+      <c r="B6" s="242" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="242" t="inlineStr">
+        <is>
+          <t>Sale Price ($)</t>
+        </is>
+      </c>
+      <c r="D6" s="242" t="inlineStr">
+        <is>
+          <t>Site Area (SF)</t>
+        </is>
+      </c>
+      <c r="E6" s="242" t="inlineStr">
+        <is>
+          <t>Sale Price ($/SF)</t>
+        </is>
+      </c>
+      <c r="F6" s="242" t="inlineStr">
+        <is>
+          <t>Sale Date</t>
+        </is>
+      </c>
+      <c r="G6" s="242" t="inlineStr">
+        <is>
+          <t>Months to Eff. Date</t>
+        </is>
+      </c>
+      <c r="H6" s="242" t="inlineStr">
+        <is>
+          <t>Monthly Mkt Rate</t>
+        </is>
+      </c>
+      <c r="I6" s="242" t="inlineStr">
+        <is>
+          <t>Time Adj %</t>
+        </is>
+      </c>
+      <c r="J6" s="242" t="inlineStr">
+        <is>
+          <t>Adjusted Price ($/SF)</t>
+        </is>
+      </c>
+      <c r="K6" s="242" t="inlineStr">
+        <is>
+          <t>Location Adj %</t>
+        </is>
+      </c>
+      <c r="L6" s="242" t="inlineStr">
+        <is>
+          <t>Topography Adj %</t>
+        </is>
+      </c>
+      <c r="M6" s="242" t="inlineStr">
+        <is>
+          <t>Surrounding Land Uses Adj %</t>
+        </is>
+      </c>
+      <c r="N6" s="242" t="inlineStr">
+        <is>
+          <t>Net Adjustment %</t>
+        </is>
+      </c>
+      <c r="O6" s="242" t="inlineStr">
+        <is>
+          <t>Indicated Value ($/SF)</t>
+        </is>
+      </c>
+      <c r="P6" s="242" t="inlineStr">
+        <is>
+          <t>Flood Zone</t>
+        </is>
+      </c>
+      <c r="Q6" s="242" t="inlineStr">
+        <is>
+          <t>Zoning</t>
+        </is>
+      </c>
+      <c r="R6" s="242" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 1</t>
+        </is>
+      </c>
+      <c r="B7" s="241" t="n"/>
+      <c r="C7" s="241" t="n"/>
+      <c r="D7" s="241" t="n"/>
+      <c r="E7" s="253">
+        <f>IF(OR(C7="",D7=""),"",C7/D7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="241" t="n"/>
+      <c r="G7" s="254">
+        <f>IF(OR(F7="",Intake!$B$9=""),"",(Intake!$B$9-F7)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H7" s="241" t="n"/>
+      <c r="I7" s="252">
+        <f>IF(OR(G7="",H7=""),"",G7*H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="253">
+        <f>IF(OR(E7="",I7=""),"",E7*(1+I7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="252" t="n"/>
+      <c r="L7" s="252" t="n"/>
+      <c r="M7" s="252" t="n"/>
+      <c r="N7" s="252">
+        <f>IF(AND(K7="",L7="",M7=""),"",SUM(K7:M7))</f>
+        <v/>
+      </c>
+      <c r="O7" s="253">
+        <f>IF(OR(J7="",N7=""),"",J7*(1+N7))</f>
+        <v/>
+      </c>
+      <c r="P7" s="241" t="n"/>
+      <c r="Q7" s="241" t="n"/>
+      <c r="R7" s="241" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 2</t>
+        </is>
+      </c>
+      <c r="B8" s="241" t="n"/>
+      <c r="C8" s="241" t="n"/>
+      <c r="D8" s="241" t="n"/>
+      <c r="E8" s="253">
+        <f>IF(OR(C8="",D8=""),"",C8/D8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="241" t="n"/>
+      <c r="G8" s="254">
+        <f>IF(OR(F8="",Intake!$B$9=""),"",(Intake!$B$9-F8)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H8" s="241" t="n"/>
+      <c r="I8" s="252">
+        <f>IF(OR(G8="",H8=""),"",G8*H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="253">
+        <f>IF(OR(E8="",I8=""),"",E8*(1+I8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="252" t="n"/>
+      <c r="L8" s="252" t="n"/>
+      <c r="M8" s="252" t="n"/>
+      <c r="N8" s="252">
+        <f>IF(AND(K8="",L8="",M8=""),"",SUM(K8:M8))</f>
+        <v/>
+      </c>
+      <c r="O8" s="253">
+        <f>IF(OR(J8="",N8=""),"",J8*(1+N8))</f>
+        <v/>
+      </c>
+      <c r="P8" s="241" t="n"/>
+      <c r="Q8" s="241" t="n"/>
+      <c r="R8" s="241" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 3</t>
+        </is>
+      </c>
+      <c r="B9" s="241" t="n"/>
+      <c r="C9" s="241" t="n"/>
+      <c r="D9" s="241" t="n"/>
+      <c r="E9" s="253">
+        <f>IF(OR(C9="",D9=""),"",C9/D9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="241" t="n"/>
+      <c r="G9" s="254">
+        <f>IF(OR(F9="",Intake!$B$9=""),"",(Intake!$B$9-F9)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H9" s="241" t="n"/>
+      <c r="I9" s="252">
+        <f>IF(OR(G9="",H9=""),"",G9*H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="253">
+        <f>IF(OR(E9="",I9=""),"",E9*(1+I9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="252" t="n"/>
+      <c r="L9" s="252" t="n"/>
+      <c r="M9" s="252" t="n"/>
+      <c r="N9" s="252">
+        <f>IF(AND(K9="",L9="",M9=""),"",SUM(K9:M9))</f>
+        <v/>
+      </c>
+      <c r="O9" s="253">
+        <f>IF(OR(J9="",N9=""),"",J9*(1+N9))</f>
+        <v/>
+      </c>
+      <c r="P9" s="241" t="n"/>
+      <c r="Q9" s="241" t="n"/>
+      <c r="R9" s="241" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 4</t>
+        </is>
+      </c>
+      <c r="B10" s="241" t="n"/>
+      <c r="C10" s="241" t="n"/>
+      <c r="D10" s="241" t="n"/>
+      <c r="E10" s="253">
+        <f>IF(OR(C10="",D10=""),"",C10/D10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="241" t="n"/>
+      <c r="G10" s="254">
+        <f>IF(OR(F10="",Intake!$B$9=""),"",(Intake!$B$9-F10)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H10" s="241" t="n"/>
+      <c r="I10" s="252">
+        <f>IF(OR(G10="",H10=""),"",G10*H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="253">
+        <f>IF(OR(E10="",I10=""),"",E10*(1+I10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="252" t="n"/>
+      <c r="L10" s="252" t="n"/>
+      <c r="M10" s="252" t="n"/>
+      <c r="N10" s="252">
+        <f>IF(AND(K10="",L10="",M10=""),"",SUM(K10:M10))</f>
+        <v/>
+      </c>
+      <c r="O10" s="253">
+        <f>IF(OR(J10="",N10=""),"",J10*(1+N10))</f>
+        <v/>
+      </c>
+      <c r="P10" s="241" t="n"/>
+      <c r="Q10" s="241" t="n"/>
+      <c r="R10" s="241" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 5</t>
+        </is>
+      </c>
+      <c r="B11" s="241" t="n"/>
+      <c r="C11" s="241" t="n"/>
+      <c r="D11" s="241" t="n"/>
+      <c r="E11" s="253">
+        <f>IF(OR(C11="",D11=""),"",C11/D11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="241" t="n"/>
+      <c r="G11" s="254">
+        <f>IF(OR(F11="",Intake!$B$9=""),"",(Intake!$B$9-F11)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H11" s="241" t="n"/>
+      <c r="I11" s="252">
+        <f>IF(OR(G11="",H11=""),"",G11*H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="253">
+        <f>IF(OR(E11="",I11=""),"",E11*(1+I11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="252" t="n"/>
+      <c r="L11" s="252" t="n"/>
+      <c r="M11" s="252" t="n"/>
+      <c r="N11" s="252">
+        <f>IF(AND(K11="",L11="",M11=""),"",SUM(K11:M11))</f>
+        <v/>
+      </c>
+      <c r="O11" s="253">
+        <f>IF(OR(J11="",N11=""),"",J11*(1+N11))</f>
+        <v/>
+      </c>
+      <c r="P11" s="241" t="n"/>
+      <c r="Q11" s="241" t="n"/>
+      <c r="R11" s="241" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 6</t>
+        </is>
+      </c>
+      <c r="B12" s="241" t="n"/>
+      <c r="C12" s="241" t="n"/>
+      <c r="D12" s="241" t="n"/>
+      <c r="E12" s="253">
+        <f>IF(OR(C12="",D12=""),"",C12/D12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="241" t="n"/>
+      <c r="G12" s="254">
+        <f>IF(OR(F12="",Intake!$B$9=""),"",(Intake!$B$9-F12)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H12" s="241" t="n"/>
+      <c r="I12" s="252">
+        <f>IF(OR(G12="",H12=""),"",G12*H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="253">
+        <f>IF(OR(E12="",I12=""),"",E12*(1+I12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="252" t="n"/>
+      <c r="L12" s="252" t="n"/>
+      <c r="M12" s="252" t="n"/>
+      <c r="N12" s="252">
+        <f>IF(AND(K12="",L12="",M12=""),"",SUM(K12:M12))</f>
+        <v/>
+      </c>
+      <c r="O12" s="253">
+        <f>IF(OR(J12="",N12=""),"",J12*(1+N12))</f>
+        <v/>
+      </c>
+      <c r="P12" s="241" t="n"/>
+      <c r="Q12" s="241" t="n"/>
+      <c r="R12" s="241" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 7</t>
+        </is>
+      </c>
+      <c r="B13" s="241" t="n"/>
+      <c r="C13" s="241" t="n"/>
+      <c r="D13" s="241" t="n"/>
+      <c r="E13" s="253">
+        <f>IF(OR(C13="",D13=""),"",C13/D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="241" t="n"/>
+      <c r="G13" s="254">
+        <f>IF(OR(F13="",Intake!$B$9=""),"",(Intake!$B$9-F13)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H13" s="241" t="n"/>
+      <c r="I13" s="252">
+        <f>IF(OR(G13="",H13=""),"",G13*H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="253">
+        <f>IF(OR(E13="",I13=""),"",E13*(1+I13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="252" t="n"/>
+      <c r="L13" s="252" t="n"/>
+      <c r="M13" s="252" t="n"/>
+      <c r="N13" s="252">
+        <f>IF(AND(K13="",L13="",M13=""),"",SUM(K13:M13))</f>
+        <v/>
+      </c>
+      <c r="O13" s="253">
+        <f>IF(OR(J13="",N13=""),"",J13*(1+N13))</f>
+        <v/>
+      </c>
+      <c r="P13" s="241" t="n"/>
+      <c r="Q13" s="241" t="n"/>
+      <c r="R13" s="241" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 8</t>
+        </is>
+      </c>
+      <c r="B14" s="241" t="n"/>
+      <c r="C14" s="241" t="n"/>
+      <c r="D14" s="241" t="n"/>
+      <c r="E14" s="253">
+        <f>IF(OR(C14="",D14=""),"",C14/D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="241" t="n"/>
+      <c r="G14" s="254">
+        <f>IF(OR(F14="",Intake!$B$9=""),"",(Intake!$B$9-F14)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H14" s="241" t="n"/>
+      <c r="I14" s="252">
+        <f>IF(OR(G14="",H14=""),"",G14*H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="253">
+        <f>IF(OR(E14="",I14=""),"",E14*(1+I14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="252" t="n"/>
+      <c r="L14" s="252" t="n"/>
+      <c r="M14" s="252" t="n"/>
+      <c r="N14" s="252">
+        <f>IF(AND(K14="",L14="",M14=""),"",SUM(K14:M14))</f>
+        <v/>
+      </c>
+      <c r="O14" s="253">
+        <f>IF(OR(J14="",N14=""),"",J14*(1+N14))</f>
+        <v/>
+      </c>
+      <c r="P14" s="241" t="n"/>
+      <c r="Q14" s="241" t="n"/>
+      <c r="R14" s="241" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 9</t>
+        </is>
+      </c>
+      <c r="B15" s="241" t="n"/>
+      <c r="C15" s="241" t="n"/>
+      <c r="D15" s="241" t="n"/>
+      <c r="E15" s="253">
+        <f>IF(OR(C15="",D15=""),"",C15/D15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="241" t="n"/>
+      <c r="G15" s="254">
+        <f>IF(OR(F15="",Intake!$B$9=""),"",(Intake!$B$9-F15)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H15" s="241" t="n"/>
+      <c r="I15" s="252">
+        <f>IF(OR(G15="",H15=""),"",G15*H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="253">
+        <f>IF(OR(E15="",I15=""),"",E15*(1+I15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="252" t="n"/>
+      <c r="L15" s="252" t="n"/>
+      <c r="M15" s="252" t="n"/>
+      <c r="N15" s="252">
+        <f>IF(AND(K15="",L15="",M15=""),"",SUM(K15:M15))</f>
+        <v/>
+      </c>
+      <c r="O15" s="253">
+        <f>IF(OR(J15="",N15=""),"",J15*(1+N15))</f>
+        <v/>
+      </c>
+      <c r="P15" s="241" t="n"/>
+      <c r="Q15" s="241" t="n"/>
+      <c r="R15" s="241" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 10</t>
+        </is>
+      </c>
+      <c r="B16" s="241" t="n"/>
+      <c r="C16" s="241" t="n"/>
+      <c r="D16" s="241" t="n"/>
+      <c r="E16" s="253">
+        <f>IF(OR(C16="",D16=""),"",C16/D16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="241" t="n"/>
+      <c r="G16" s="254">
+        <f>IF(OR(F16="",Intake!$B$9=""),"",(Intake!$B$9-F16)/30.4375)</f>
+        <v/>
+      </c>
+      <c r="H16" s="241" t="n"/>
+      <c r="I16" s="252">
+        <f>IF(OR(G16="",H16=""),"",G16*H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="253">
+        <f>IF(OR(E16="",I16=""),"",E16*(1+I16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="252" t="n"/>
+      <c r="L16" s="252" t="n"/>
+      <c r="M16" s="252" t="n"/>
+      <c r="N16" s="252">
+        <f>IF(AND(K16="",L16="",M16=""),"",SUM(K16:M16))</f>
+        <v/>
+      </c>
+      <c r="O16" s="253">
+        <f>IF(OR(J16="",N16=""),"",J16*(1+N16))</f>
+        <v/>
+      </c>
+      <c r="P16" s="241" t="n"/>
+      <c r="Q16" s="241" t="n"/>
+      <c r="R16" s="241" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="255" t="inlineStr">
+        <is>
+          <t>MEAN</t>
+        </is>
+      </c>
+      <c r="E17" s="256">
+        <f>IFERROR(AVERAGE(E7:E16),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="256">
+        <f>IFERROR(AVERAGE(J7:J16),"")</f>
+        <v/>
+      </c>
+      <c r="O17" s="256">
+        <f>IFERROR(AVERAGE(O7:O16),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="242" t="inlineStr">
+        <is>
+          <t>LAND VALUE CONCLUSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Indicated Range ($/SF):</t>
+        </is>
+      </c>
+      <c r="B20" s="256">
+        <f>IFERROR(MIN(O7:O16),"")</f>
+        <v/>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D20" s="256">
+        <f>IFERROR(MAX(O7:O16),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Concluded Land Value ($/SF):</t>
+        </is>
+      </c>
+      <c r="B21" s="253" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Site Area (SF):</t>
+        </is>
+      </c>
+      <c r="B22" s="241" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Concluded Land Value:</t>
+        </is>
+      </c>
+      <c r="B23" s="257">
+        <f>B21*B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Green cells = manual entry. Enter adjustment % as a fraction (e.g. 0.05 for +5%). Narrative AI reads this tab at deliver time.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -13046,809 +13332,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.19999980926514"/>
-  <cols>
-    <col width="2" customWidth="1" style="160" min="1" max="1"/>
-    <col width="13.5546875" customWidth="1" style="160" min="2" max="2"/>
-    <col width="28" customWidth="1" style="160" min="3" max="3"/>
-    <col width="12" customWidth="1" style="160" min="4" max="4"/>
-    <col width="14" customWidth="1" style="160" min="5" max="6"/>
-    <col width="12" customWidth="1" style="160" min="7" max="7"/>
-    <col width="10" customWidth="1" style="160" min="8" max="8"/>
-    <col width="8" customWidth="1" style="160" min="9" max="9"/>
-    <col width="12" customWidth="1" style="160" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="6" customHeight="1" s="160"/>
-    <row r="2" ht="18" customHeight="1" s="160">
-      <c r="B2" s="236" t="inlineStr">
-        <is>
-          <t>COMPARABLE LAND SALES — SUMMARY</t>
-        </is>
-      </c>
-      <c r="C2" s="162" t="n"/>
-      <c r="D2" s="162" t="n"/>
-      <c r="E2" s="162" t="n"/>
-      <c r="F2" s="162" t="n"/>
-      <c r="G2" s="162" t="n"/>
-      <c r="H2" s="162" t="n"/>
-      <c r="I2" s="162" t="n"/>
-      <c r="J2" s="163" t="n"/>
-    </row>
-    <row r="3" ht="13.94999980926514" customHeight="1" s="160">
-      <c r="B3" s="237" t="inlineStr">
-        <is>
-          <t>Subject: 100 Example Commerce Way, Sample City — 55,452 SF (1.27 Ac), Zone X, C-5</t>
-        </is>
-      </c>
-      <c r="C3" s="162" t="n"/>
-      <c r="D3" s="162" t="n"/>
-      <c r="E3" s="162" t="n"/>
-      <c r="F3" s="162" t="n"/>
-      <c r="G3" s="162" t="n"/>
-      <c r="H3" s="162" t="n"/>
-      <c r="I3" s="162" t="n"/>
-      <c r="J3" s="163" t="n"/>
-    </row>
-    <row r="4" ht="16.04999923706055" customHeight="1" s="160">
-      <c r="B4" s="37" t="inlineStr">
-        <is>
-          <t>Sale No.</t>
-        </is>
-      </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="inlineStr">
-        <is>
-          <t>Sale Date</t>
-        </is>
-      </c>
-      <c r="E4" s="37" t="inlineStr">
-        <is>
-          <t>Sale Price</t>
-        </is>
-      </c>
-      <c r="F4" s="37" t="inlineStr">
-        <is>
-          <t>Site Area (SF)</t>
-        </is>
-      </c>
-      <c r="G4" s="37" t="inlineStr">
-        <is>
-          <t>Price/SF</t>
-        </is>
-      </c>
-      <c r="H4" s="37" t="inlineStr">
-        <is>
-          <t>Flood Zone</t>
-        </is>
-      </c>
-      <c r="I4" s="37" t="inlineStr">
-        <is>
-          <t>Zoning</t>
-        </is>
-      </c>
-      <c r="J4" s="37" t="inlineStr">
-        <is>
-          <t>Shape</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="160">
-      <c r="B5" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="56" t="n"/>
-      <c r="D5" s="56" t="n"/>
-      <c r="E5" s="57" t="n"/>
-      <c r="F5" s="57" t="n"/>
-      <c r="G5" s="57">
-        <f>E5/F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="57" t="n"/>
-      <c r="I5" s="57" t="n"/>
-      <c r="J5" s="57" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="160">
-      <c r="B6" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="58" t="n"/>
-      <c r="D6" s="58" t="n"/>
-      <c r="E6" s="59" t="n"/>
-      <c r="F6" s="59" t="n"/>
-      <c r="G6" s="59">
-        <f>E6/F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="59" t="n"/>
-      <c r="I6" s="59" t="n"/>
-      <c r="J6" s="59" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="160">
-      <c r="B7" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="56" t="n"/>
-      <c r="D7" s="56" t="n"/>
-      <c r="E7" s="57" t="n"/>
-      <c r="F7" s="57" t="n"/>
-      <c r="G7" s="57">
-        <f>E7/F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="57" t="n"/>
-      <c r="I7" s="57" t="n"/>
-      <c r="J7" s="57" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="160">
-      <c r="B8" s="58" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="58" t="n"/>
-      <c r="D8" s="58" t="n"/>
-      <c r="E8" s="59" t="n"/>
-      <c r="F8" s="59" t="n"/>
-      <c r="G8" s="59">
-        <f>E8/F8</f>
-        <v/>
-      </c>
-      <c r="H8" s="59" t="n"/>
-      <c r="I8" s="59" t="n"/>
-      <c r="J8" s="59" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="160">
-      <c r="B9" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="56" t="n"/>
-      <c r="D9" s="56" t="n"/>
-      <c r="E9" s="57" t="n"/>
-      <c r="F9" s="57" t="n"/>
-      <c r="G9" s="57">
-        <f>E9/F9</f>
-        <v/>
-      </c>
-      <c r="H9" s="57" t="n"/>
-      <c r="I9" s="57" t="n"/>
-      <c r="J9" s="57" t="n"/>
-    </row>
-    <row r="10" ht="16.04999923706055" customHeight="1" s="160">
-      <c r="B10" s="60" t="inlineStr">
-        <is>
-          <t>MEAN</t>
-        </is>
-      </c>
-      <c r="C10" s="61" t="n"/>
-      <c r="D10" s="61" t="n"/>
-      <c r="E10" s="61">
-        <f>AVERAGE(E5:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="61">
-        <f>AVERAGE(F5:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="61">
-        <f>AVERAGE(G5:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="61" t="n"/>
-      <c r="I10" s="61" t="n"/>
-      <c r="J10" s="61" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="160">
-      <c r="B11" s="62" t="inlineStr">
-        <is>
-          <t>SUBJECT</t>
-        </is>
-      </c>
-      <c r="C11" s="63" t="n"/>
-      <c r="D11" s="63" t="n"/>
-      <c r="E11" s="63" t="n"/>
-      <c r="F11" s="64" t="n"/>
-      <c r="G11" s="64" t="n"/>
-      <c r="H11" s="64" t="n"/>
-      <c r="I11" s="64" t="n"/>
-      <c r="J11" s="64" t="n"/>
-    </row>
-    <row r="12" ht="6" customHeight="1" s="160"/>
-    <row r="13" ht="18" customHeight="1" s="160">
-      <c r="B13" s="236" t="inlineStr">
-        <is>
-          <t>LAND SALES ADJUSTMENT GRID</t>
-        </is>
-      </c>
-      <c r="C13" s="162" t="n"/>
-      <c r="D13" s="162" t="n"/>
-      <c r="E13" s="162" t="n"/>
-      <c r="F13" s="162" t="n"/>
-      <c r="G13" s="162" t="n"/>
-      <c r="H13" s="162" t="n"/>
-      <c r="I13" s="162" t="n"/>
-      <c r="J13" s="163" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="160">
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>Sale No.</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>Sale Date</t>
-        </is>
-      </c>
-      <c r="D14" s="37" t="inlineStr">
-        <is>
-          <t>Price/SF</t>
-        </is>
-      </c>
-      <c r="E14" s="37" t="inlineStr">
-        <is>
-          <t>Mkt Cond Adj.</t>
-        </is>
-      </c>
-      <c r="F14" s="37" t="inlineStr">
-        <is>
-          <t>Adj. Price/SF</t>
-        </is>
-      </c>
-      <c r="G14" s="37" t="inlineStr">
-        <is>
-          <t>Size Adj.</t>
-        </is>
-      </c>
-      <c r="H14" s="37" t="inlineStr">
-        <is>
-          <t>Location Adj.</t>
-        </is>
-      </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>Net Adj.</t>
-        </is>
-      </c>
-      <c r="J14" s="37" t="inlineStr">
-        <is>
-          <t>Indicated $/SF</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="160">
-      <c r="B15" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="56" t="n"/>
-      <c r="D15" s="57" t="n"/>
-      <c r="E15" s="65" t="n"/>
-      <c r="F15" s="57">
-        <f>D15*(1+E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="65" t="n"/>
-      <c r="H15" s="65" t="n"/>
-      <c r="I15" s="65" t="n"/>
-      <c r="J15" s="65">
-        <f>F15*(1+I15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="160">
-      <c r="B16" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="58" t="n"/>
-      <c r="D16" s="59" t="n"/>
-      <c r="E16" s="65" t="n"/>
-      <c r="F16" s="59">
-        <f>D16*(1+E16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="65" t="n"/>
-      <c r="H16" s="65" t="n"/>
-      <c r="I16" s="65" t="n"/>
-      <c r="J16" s="65">
-        <f>F16*(1+I16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="160">
-      <c r="B17" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="56" t="n"/>
-      <c r="D17" s="57" t="n"/>
-      <c r="E17" s="65" t="n"/>
-      <c r="F17" s="57">
-        <f>D17*(1+E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="65" t="n"/>
-      <c r="H17" s="65" t="n"/>
-      <c r="I17" s="65" t="n"/>
-      <c r="J17" s="65">
-        <f>F17*(1+I17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="160">
-      <c r="B18" s="58" t="n">
-        <v>4</v>
-      </c>
-      <c r="C18" s="58" t="n"/>
-      <c r="D18" s="59" t="n"/>
-      <c r="E18" s="65" t="n"/>
-      <c r="F18" s="59">
-        <f>D18*(1+E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="65" t="n"/>
-      <c r="H18" s="65" t="n"/>
-      <c r="I18" s="65" t="n"/>
-      <c r="J18" s="65">
-        <f>F18*(1+I18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="160">
-      <c r="B19" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" s="56" t="n"/>
-      <c r="D19" s="57" t="n"/>
-      <c r="E19" s="65" t="n"/>
-      <c r="F19" s="57">
-        <f>D19*(1+E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="65" t="n"/>
-      <c r="H19" s="65" t="n"/>
-      <c r="I19" s="65" t="n"/>
-      <c r="J19" s="65">
-        <f>F19*(1+I19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16.04999923706055" customHeight="1" s="160">
-      <c r="B20" s="60" t="inlineStr">
-        <is>
-          <t>MEAN</t>
-        </is>
-      </c>
-      <c r="C20" s="61" t="n"/>
-      <c r="D20" s="61">
-        <f>AVERAGE(D15:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="61" t="n"/>
-      <c r="F20" s="61">
-        <f>AVERAGE(F15:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="61" t="n"/>
-      <c r="H20" s="61" t="n"/>
-      <c r="I20" s="61" t="n"/>
-      <c r="J20" s="61">
-        <f>AVERAGE(J15:J19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="6" customHeight="1" s="160"/>
-    <row r="22" ht="18" customHeight="1" s="160">
-      <c r="B22" s="236" t="inlineStr">
-        <is>
-          <t>LAND VALUE CONCLUSION</t>
-        </is>
-      </c>
-      <c r="C22" s="162" t="n"/>
-      <c r="D22" s="162" t="n"/>
-      <c r="E22" s="162" t="n"/>
-      <c r="F22" s="162" t="n"/>
-      <c r="G22" s="162" t="n"/>
-      <c r="H22" s="162" t="n"/>
-      <c r="I22" s="162" t="n"/>
-      <c r="J22" s="163" t="n"/>
-    </row>
-    <row r="23" ht="28.79999923706055" customHeight="1" s="160">
-      <c r="B23" s="56" t="inlineStr">
-        <is>
-          <t>Indicated Range ($/SF):</t>
-        </is>
-      </c>
-      <c r="C23" s="56" t="n"/>
-      <c r="D23" s="65">
-        <f>MIN(J15:J19)</f>
-        <v/>
-      </c>
-      <c r="E23" s="57" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="F23" s="57">
-        <f>MAX(J15:J19)</f>
-        <v/>
-      </c>
-      <c r="G23" s="57" t="n"/>
-      <c r="H23" s="57" t="n"/>
-      <c r="I23" s="57" t="n"/>
-      <c r="J23" s="57" t="n"/>
-    </row>
-    <row r="24" ht="40.20000076293945" customHeight="1" s="160">
-      <c r="B24" s="58" t="inlineStr">
-        <is>
-          <t>Concluded Land Value ($/SF):</t>
-        </is>
-      </c>
-      <c r="C24" s="58" t="n"/>
-      <c r="D24" s="65" t="n"/>
-      <c r="E24" s="59" t="n"/>
-      <c r="F24" s="59" t="n"/>
-      <c r="G24" s="59" t="n"/>
-      <c r="H24" s="59" t="n"/>
-      <c r="I24" s="59" t="n"/>
-      <c r="J24" s="59" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="160">
-      <c r="B25" s="56" t="inlineStr">
-        <is>
-          <t>Site Area (SF):</t>
-        </is>
-      </c>
-      <c r="C25" s="56" t="n"/>
-      <c r="D25" s="65" t="n"/>
-      <c r="E25" s="57" t="n"/>
-      <c r="F25" s="57" t="n"/>
-      <c r="G25" s="57" t="n"/>
-      <c r="H25" s="57" t="n"/>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="57" t="n"/>
-    </row>
-    <row r="26" ht="33.59999847412109" customHeight="1" s="160">
-      <c r="B26" s="66" t="inlineStr">
-        <is>
-          <t>Concluded Land Value:</t>
-        </is>
-      </c>
-      <c r="C26" s="66" t="n"/>
-      <c r="D26" s="67">
-        <f>D24*D25</f>
-        <v/>
-      </c>
-      <c r="E26" s="67" t="n"/>
-      <c r="F26" s="67" t="n"/>
-      <c r="G26" s="67" t="n"/>
-      <c r="H26" s="67" t="n"/>
-      <c r="I26" s="67" t="n"/>
-      <c r="J26" s="67" t="n"/>
-    </row>
-    <row r="27" ht="6" customHeight="1" s="160"/>
-    <row r="28" ht="18" customHeight="1" s="160">
-      <c r="B28" s="236" t="inlineStr">
-        <is>
-          <t>LAND SALES — ADJUSTMENT INPUTS</t>
-        </is>
-      </c>
-      <c r="C28" s="162" t="n"/>
-      <c r="D28" s="162" t="n"/>
-      <c r="E28" s="162" t="n"/>
-      <c r="F28" s="162" t="n"/>
-      <c r="G28" s="162" t="n"/>
-      <c r="H28" s="162" t="n"/>
-      <c r="I28" s="162" t="n"/>
-      <c r="J28" s="163" t="n"/>
-    </row>
-    <row r="29" ht="28.04999923706055" customHeight="1" s="160">
-      <c r="B29" s="234" t="inlineStr">
-        <is>
-          <t>Enter adjustment % for each comp (positive = upward, negative = downward, 0 = no adjustment). Notes are optional; used by AI narrative generator.</t>
-        </is>
-      </c>
-      <c r="C29" s="162" t="n"/>
-      <c r="D29" s="162" t="n"/>
-      <c r="E29" s="162" t="n"/>
-      <c r="F29" s="162" t="n"/>
-      <c r="G29" s="162" t="n"/>
-      <c r="H29" s="162" t="n"/>
-      <c r="I29" s="162" t="n"/>
-      <c r="J29" s="163" t="n"/>
-    </row>
-    <row r="30" ht="37.79999923706055" customHeight="1" s="160">
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>Comp No.</t>
-        </is>
-      </c>
-      <c r="C30" s="37" t="inlineStr">
-        <is>
-          <t>Location (auto-ref)</t>
-        </is>
-      </c>
-      <c r="D30" s="37" t="inlineStr">
-        <is>
-          <t>Mkt Cond
-Adj %</t>
-        </is>
-      </c>
-      <c r="E30" s="37" t="inlineStr">
-        <is>
-          <t>Mkt Cond
-Note</t>
-        </is>
-      </c>
-      <c r="F30" s="37" t="inlineStr">
-        <is>
-          <t>Location
-Adj %</t>
-        </is>
-      </c>
-      <c r="G30" s="37" t="inlineStr">
-        <is>
-          <t>Location
-Note</t>
-        </is>
-      </c>
-      <c r="H30" s="37" t="inlineStr">
-        <is>
-          <t>Other
-Adj %</t>
-        </is>
-      </c>
-      <c r="I30" s="37" t="inlineStr">
-        <is>
-          <t>Other
-Note</t>
-        </is>
-      </c>
-      <c r="J30" s="37" t="inlineStr">
-        <is>
-          <t>Dilmore
-Size Adj %</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="160">
-      <c r="B31" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="56" t="inlineStr">
-        <is>
-          <t>Comp 1 Address</t>
-        </is>
-      </c>
-      <c r="D31" s="65" t="n"/>
-      <c r="E31" s="68" t="n"/>
-      <c r="F31" s="65" t="n"/>
-      <c r="G31" s="68" t="n"/>
-      <c r="H31" s="65" t="n"/>
-      <c r="I31" s="68" t="n"/>
-      <c r="J31" s="68">
-        <f>IFERROR(size_adj!D6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="160">
-      <c r="B32" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="58" t="inlineStr">
-        <is>
-          <t>Comp 2 Address</t>
-        </is>
-      </c>
-      <c r="D32" s="65" t="n"/>
-      <c r="E32" s="68" t="n"/>
-      <c r="F32" s="65" t="n"/>
-      <c r="G32" s="68" t="n"/>
-      <c r="H32" s="65" t="n"/>
-      <c r="I32" s="68" t="n"/>
-      <c r="J32" s="68">
-        <f>IFERROR(size_adj!D7,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="160">
-      <c r="B33" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="56" t="inlineStr">
-        <is>
-          <t>Comp 3 Address</t>
-        </is>
-      </c>
-      <c r="D33" s="65" t="n"/>
-      <c r="E33" s="68" t="n"/>
-      <c r="F33" s="65" t="n"/>
-      <c r="G33" s="68" t="n"/>
-      <c r="H33" s="65" t="n"/>
-      <c r="I33" s="68" t="n"/>
-      <c r="J33" s="68">
-        <f>IFERROR(size_adj!D8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="160">
-      <c r="B34" s="58" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" s="58" t="inlineStr">
-        <is>
-          <t>Comp 4 Address</t>
-        </is>
-      </c>
-      <c r="D34" s="65" t="n"/>
-      <c r="E34" s="68" t="n"/>
-      <c r="F34" s="65" t="n"/>
-      <c r="G34" s="68" t="n"/>
-      <c r="H34" s="65" t="n"/>
-      <c r="I34" s="68" t="n"/>
-      <c r="J34" s="68">
-        <f>IFERROR(size_adj!D9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="160">
-      <c r="B35" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" s="56" t="inlineStr">
-        <is>
-          <t>Comp 5 Address</t>
-        </is>
-      </c>
-      <c r="D35" s="65" t="n"/>
-      <c r="E35" s="68" t="n"/>
-      <c r="F35" s="65" t="n"/>
-      <c r="G35" s="68" t="n"/>
-      <c r="H35" s="65" t="n"/>
-      <c r="I35" s="68" t="n"/>
-      <c r="J35" s="68">
-        <f>IFERROR(size_adj!D10,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="160">
-      <c r="B36" s="58" t="n">
-        <v>6</v>
-      </c>
-      <c r="C36" s="58" t="inlineStr">
-        <is>
-          <t>Comp 6 Address</t>
-        </is>
-      </c>
-      <c r="D36" s="65" t="n"/>
-      <c r="E36" s="68" t="n"/>
-      <c r="F36" s="65" t="n"/>
-      <c r="G36" s="68" t="n"/>
-      <c r="H36" s="65" t="n"/>
-      <c r="I36" s="68" t="n"/>
-      <c r="J36" s="68">
-        <f>IFERROR(size_adj!D11,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="160">
-      <c r="B37" s="56" t="n">
-        <v>7</v>
-      </c>
-      <c r="C37" s="56" t="inlineStr">
-        <is>
-          <t>Comp 7 Address</t>
-        </is>
-      </c>
-      <c r="D37" s="65" t="n"/>
-      <c r="E37" s="68" t="n"/>
-      <c r="F37" s="65" t="n"/>
-      <c r="G37" s="68" t="n"/>
-      <c r="H37" s="65" t="n"/>
-      <c r="I37" s="68" t="n"/>
-      <c r="J37" s="68">
-        <f>IFERROR(size_adj!D12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="160">
-      <c r="B38" s="58" t="n">
-        <v>8</v>
-      </c>
-      <c r="C38" s="58" t="inlineStr">
-        <is>
-          <t>Comp 8 Address</t>
-        </is>
-      </c>
-      <c r="D38" s="65" t="n"/>
-      <c r="E38" s="68" t="n"/>
-      <c r="F38" s="65" t="n"/>
-      <c r="G38" s="68" t="n"/>
-      <c r="H38" s="65" t="n"/>
-      <c r="I38" s="68" t="n"/>
-      <c r="J38" s="68">
-        <f>IFERROR(size_adj!D13,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="160">
-      <c r="B39" s="56" t="n">
-        <v>9</v>
-      </c>
-      <c r="C39" s="56" t="inlineStr">
-        <is>
-          <t>Comp 9 Address</t>
-        </is>
-      </c>
-      <c r="D39" s="65" t="n"/>
-      <c r="E39" s="68" t="n"/>
-      <c r="F39" s="65" t="n"/>
-      <c r="G39" s="68" t="n"/>
-      <c r="H39" s="65" t="n"/>
-      <c r="I39" s="68" t="n"/>
-      <c r="J39" s="68">
-        <f>IFERROR(size_adj!D14,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="160">
-      <c r="B40" s="58" t="n">
-        <v>10</v>
-      </c>
-      <c r="C40" s="58" t="inlineStr">
-        <is>
-          <t>Comp 10 Address</t>
-        </is>
-      </c>
-      <c r="D40" s="65" t="n"/>
-      <c r="E40" s="68" t="n"/>
-      <c r="F40" s="65" t="n"/>
-      <c r="G40" s="68" t="n"/>
-      <c r="H40" s="65" t="n"/>
-      <c r="I40" s="68" t="n"/>
-      <c r="J40" s="68">
-        <f>IFERROR(size_adj!D15,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="6" customHeight="1" s="160"/>
-    <row r="42" ht="13.94999980926514" customHeight="1" s="160">
-      <c r="B42" s="238" t="inlineStr">
-        <is>
-          <t>Note: Adjustment % should match values in the MARKET CHART adjustment grid. Narrative AI reads these inputs at deliver time.</t>
-        </is>
-      </c>
-      <c r="C42" s="162" t="n"/>
-      <c r="D42" s="162" t="n"/>
-      <c r="E42" s="162" t="n"/>
-      <c r="F42" s="162" t="n"/>
-      <c r="G42" s="162" t="n"/>
-      <c r="H42" s="162" t="n"/>
-      <c r="I42" s="162" t="n"/>
-      <c r="J42" s="163" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B2:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.19999980926514"/>
   <cols>
@@ -14831,7 +14314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14999,7 +14482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15132,7 +14615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15452,7 +14935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15708,7 +15191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15939,4 +15422,363 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.19999980926514"/>
+  <cols>
+    <col width="2" customWidth="1" style="160" min="1" max="1"/>
+    <col width="22" customWidth="1" style="160" min="2" max="2"/>
+    <col width="40.6640625" customWidth="1" style="160" min="3" max="3"/>
+    <col width="12" customWidth="1" style="160" min="4" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="6" customHeight="1" s="160"/>
+    <row r="2" ht="18" customHeight="1" s="160">
+      <c r="B2" s="236" t="inlineStr">
+        <is>
+          <t>LEASE COMPARABLE — QUALITATIVE ANALYSIS</t>
+        </is>
+      </c>
+      <c r="C2" s="162" t="n"/>
+      <c r="D2" s="162" t="n"/>
+      <c r="E2" s="162" t="n"/>
+      <c r="F2" s="162" t="n"/>
+      <c r="G2" s="162" t="n"/>
+      <c r="H2" s="162" t="n"/>
+      <c r="I2" s="162" t="n"/>
+      <c r="J2" s="163" t="n"/>
+    </row>
+    <row r="3" ht="13.94999980926514" customHeight="1" s="160">
+      <c r="B3" s="239" t="n"/>
+      <c r="C3" s="162" t="n"/>
+      <c r="D3" s="162" t="n"/>
+      <c r="E3" s="162" t="n"/>
+      <c r="F3" s="162" t="n"/>
+      <c r="G3" s="162" t="n"/>
+      <c r="H3" s="162" t="n"/>
+      <c r="I3" s="162" t="n"/>
+      <c r="J3" s="163" t="n"/>
+    </row>
+    <row r="4" ht="16.04999923706055" customHeight="1" s="160">
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>Comp No.</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>Rate ($/SF)</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>Lease Terms</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="160">
+      <c r="B5" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="56" t="n"/>
+      <c r="D5" s="75" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="G5" s="41" t="n"/>
+      <c r="H5" s="41" t="n"/>
+      <c r="I5" s="41" t="n"/>
+      <c r="J5" s="41" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="160">
+      <c r="B6" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="58" t="n"/>
+      <c r="D6" s="78" t="n"/>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="44" t="n"/>
+      <c r="H6" s="99" t="n"/>
+      <c r="I6" s="100" t="n"/>
+      <c r="J6" s="44" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="160">
+      <c r="B7" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="56" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="41" t="n"/>
+      <c r="H7" s="41" t="n"/>
+      <c r="I7" s="41" t="n"/>
+      <c r="J7" s="41" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="160">
+      <c r="B8" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="58" t="n"/>
+      <c r="D8" s="78" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="99" t="n"/>
+      <c r="I8" s="100" t="n"/>
+      <c r="J8" s="44" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="160">
+      <c r="B9" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="56" t="n"/>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="41" t="n"/>
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="41" t="n"/>
+      <c r="H9" s="41" t="n"/>
+      <c r="I9" s="41" t="n"/>
+      <c r="J9" s="99" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="160">
+      <c r="B10" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="58" t="n"/>
+      <c r="D10" s="78" t="n"/>
+      <c r="E10" s="99" t="n"/>
+      <c r="F10" s="99" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="99" t="n"/>
+      <c r="I10" s="100" t="n"/>
+      <c r="J10" s="99" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="160">
+      <c r="B11" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="56" t="n"/>
+      <c r="D11" s="75" t="n"/>
+      <c r="E11" s="100" t="n"/>
+      <c r="F11" s="41" t="n"/>
+      <c r="G11" s="41" t="n"/>
+      <c r="H11" s="41" t="n"/>
+      <c r="I11" s="41" t="n"/>
+      <c r="J11" s="100" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="160">
+      <c r="B12" s="58" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="58" t="n"/>
+      <c r="D12" s="78" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="99" t="n"/>
+      <c r="G12" s="99" t="n"/>
+      <c r="H12" s="100" t="n"/>
+      <c r="I12" s="44" t="n"/>
+      <c r="J12" s="99" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="160">
+      <c r="B13" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="56" t="n"/>
+      <c r="D13" s="75" t="n"/>
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="99" t="n"/>
+      <c r="I13" s="41" t="n"/>
+      <c r="J13" s="99" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="160">
+      <c r="B14" s="58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="58" t="n"/>
+      <c r="D14" s="78" t="n"/>
+      <c r="E14" s="99" t="n"/>
+      <c r="F14" s="99" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="100" t="n"/>
+      <c r="I14" s="100" t="n"/>
+      <c r="J14" s="99" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="160">
+      <c r="B15" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="56" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="41" t="n"/>
+      <c r="G15" s="41" t="n"/>
+      <c r="H15" s="99" t="n"/>
+      <c r="I15" s="100" t="n"/>
+      <c r="J15" s="41" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="160">
+      <c r="B16" s="58" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="78" t="n"/>
+      <c r="E16" s="100" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="44" t="n"/>
+      <c r="H16" s="99" t="n"/>
+      <c r="I16" s="100" t="n"/>
+      <c r="J16" s="100" t="n"/>
+    </row>
+    <row r="17" ht="6" customHeight="1" s="160"/>
+    <row r="18" ht="18" customHeight="1" s="160">
+      <c r="B18" s="236" t="inlineStr">
+        <is>
+          <t>MARKET RENT CONCLUSION</t>
+        </is>
+      </c>
+      <c r="C18" s="162" t="n"/>
+      <c r="D18" s="162" t="n"/>
+      <c r="E18" s="162" t="n"/>
+      <c r="F18" s="162" t="n"/>
+      <c r="G18" s="162" t="n"/>
+      <c r="H18" s="162" t="n"/>
+      <c r="I18" s="162" t="n"/>
+      <c r="J18" s="163" t="n"/>
+    </row>
+    <row r="19" ht="28.20000076293945" customHeight="1" s="160">
+      <c r="B19" s="56" t="inlineStr">
+        <is>
+          <t>Range of Comparable Rates:</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="n"/>
+      <c r="D19" s="56" t="n"/>
+      <c r="E19" s="56" t="n"/>
+      <c r="F19" s="56" t="n"/>
+      <c r="G19" s="56" t="n"/>
+      <c r="H19" s="56" t="n"/>
+      <c r="I19" s="56" t="n"/>
+      <c r="J19" s="56" t="n"/>
+    </row>
+    <row r="20" ht="35.40000152587891" customHeight="1" s="160">
+      <c r="B20" s="198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most Comparable Comps </t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="58" t="n"/>
+      <c r="H20" s="58" t="n"/>
+      <c r="I20" s="58" t="n"/>
+      <c r="J20" s="58" t="n"/>
+    </row>
+    <row r="21" ht="35.40000152587891" customHeight="1" s="160">
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>Size Adjustment:</t>
+        </is>
+      </c>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="58" t="n"/>
+      <c r="I21" s="58" t="n"/>
+      <c r="J21" s="58" t="n"/>
+    </row>
+    <row r="22" ht="37.20000076293945" customHeight="1" s="160">
+      <c r="B22" s="56" t="inlineStr">
+        <is>
+          <t>Concluded Market Rent:</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="n"/>
+      <c r="D22" s="56" t="n"/>
+      <c r="E22" s="56" t="n"/>
+      <c r="F22" s="56" t="n"/>
+      <c r="G22" s="56" t="n"/>
+      <c r="H22" s="56" t="n"/>
+      <c r="I22" s="56" t="n"/>
+      <c r="J22" s="56" t="n"/>
+    </row>
+    <row r="23" ht="6" customHeight="1" s="160"/>
+    <row r="24" ht="13.94999980926514" customHeight="1" s="160">
+      <c r="B24" s="62" t="inlineStr">
+        <is>
+          <t>Color Key:</t>
+        </is>
+      </c>
+      <c r="C24" s="62" t="inlineStr">
+        <is>
+          <t>Superior</t>
+        </is>
+      </c>
+      <c r="D24" s="62" t="inlineStr">
+        <is>
+          <t>Similar</t>
+        </is>
+      </c>
+      <c r="E24" s="62" t="inlineStr">
+        <is>
+          <t>Inferior</t>
+        </is>
+      </c>
+      <c r="F24" s="62" t="n"/>
+      <c r="G24" s="62" t="n"/>
+      <c r="H24" s="62" t="n"/>
+      <c r="I24" s="62" t="n"/>
+      <c r="J24" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/templates/workbook.xlsx
+++ b/templates/workbook.xlsx
@@ -20,6 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dilmore" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sca_adjustment_grid" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="land_adjustment_grid" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sca_qualitative" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="land_qualitative" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -562,7 +564,7 @@
     <xf numFmtId="9" fontId="18" fillId="0" borderId="8"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="8"/>
   </cellStyleXfs>
-  <cellXfs count="258">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1225,6 +1227,8 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0"/>
@@ -11911,6 +11915,782 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="160" min="1" max="1"/>
+    <col width="20" customWidth="1" style="160" min="2" max="2"/>
+    <col width="12" customWidth="1" style="160" min="3" max="3"/>
+    <col width="12" customWidth="1" style="160" min="4" max="4"/>
+    <col width="12" customWidth="1" style="160" min="5" max="5"/>
+    <col width="12" customWidth="1" style="160" min="6" max="6"/>
+    <col width="12" customWidth="1" style="160" min="7" max="7"/>
+    <col width="12" customWidth="1" style="160" min="8" max="8"/>
+    <col width="12" customWidth="1" style="160" min="9" max="9"/>
+    <col width="12" customWidth="1" style="160" min="10" max="10"/>
+    <col width="12" customWidth="1" style="160" min="11" max="11"/>
+    <col width="12" customWidth="1" style="160" min="12" max="12"/>
+    <col width="10" customWidth="1" style="160" min="13" max="13"/>
+    <col width="11" customWidth="1" style="160" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Qualitative Analysis Grid — Sales Comparison Approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Threshold (|Overall| below this = Similar):</t>
+        </is>
+      </c>
+      <c r="B3" s="241" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>← Retune Superior/Similar/Inferior sensitivity here, per assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="242" t="inlineStr">
+        <is>
+          <t>Comp</t>
+        </is>
+      </c>
+      <c r="B6" s="242" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="242" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="D6" s="242" t="inlineStr">
+        <is>
+          <t>MHI</t>
+        </is>
+      </c>
+      <c r="E6" s="242" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="F6" s="242" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="G6" s="242" t="inlineStr">
+        <is>
+          <t>Visibility</t>
+        </is>
+      </c>
+      <c r="H6" s="242" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="I6" s="242" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="J6" s="242" t="inlineStr">
+        <is>
+          <t>Flood Zone</t>
+        </is>
+      </c>
+      <c r="K6" s="242" t="inlineStr">
+        <is>
+          <t>LTB</t>
+        </is>
+      </c>
+      <c r="L6" s="242" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="M6" s="242" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="N6" s="242" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 1</t>
+        </is>
+      </c>
+      <c r="B7" s="241" t="n"/>
+      <c r="C7" s="258" t="n"/>
+      <c r="D7" s="258" t="n"/>
+      <c r="E7" s="258" t="n"/>
+      <c r="F7" s="258" t="n"/>
+      <c r="G7" s="258" t="n"/>
+      <c r="H7" s="258" t="n"/>
+      <c r="I7" s="258" t="n"/>
+      <c r="J7" s="258" t="n"/>
+      <c r="K7" s="258" t="n"/>
+      <c r="L7" s="258" t="n"/>
+      <c r="M7" s="259">
+        <f>IFERROR(AVERAGE(C7:L7),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="241">
+        <f>IF(M7="","",IF(M7&gt;$B$3,"Superior",IF(M7&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 2</t>
+        </is>
+      </c>
+      <c r="B8" s="241" t="n"/>
+      <c r="C8" s="258" t="n"/>
+      <c r="D8" s="258" t="n"/>
+      <c r="E8" s="258" t="n"/>
+      <c r="F8" s="258" t="n"/>
+      <c r="G8" s="258" t="n"/>
+      <c r="H8" s="258" t="n"/>
+      <c r="I8" s="258" t="n"/>
+      <c r="J8" s="258" t="n"/>
+      <c r="K8" s="258" t="n"/>
+      <c r="L8" s="258" t="n"/>
+      <c r="M8" s="259">
+        <f>IFERROR(AVERAGE(C8:L8),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="241">
+        <f>IF(M8="","",IF(M8&gt;$B$3,"Superior",IF(M8&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 3</t>
+        </is>
+      </c>
+      <c r="B9" s="241" t="n"/>
+      <c r="C9" s="258" t="n"/>
+      <c r="D9" s="258" t="n"/>
+      <c r="E9" s="258" t="n"/>
+      <c r="F9" s="258" t="n"/>
+      <c r="G9" s="258" t="n"/>
+      <c r="H9" s="258" t="n"/>
+      <c r="I9" s="258" t="n"/>
+      <c r="J9" s="258" t="n"/>
+      <c r="K9" s="258" t="n"/>
+      <c r="L9" s="258" t="n"/>
+      <c r="M9" s="259">
+        <f>IFERROR(AVERAGE(C9:L9),"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="241">
+        <f>IF(M9="","",IF(M9&gt;$B$3,"Superior",IF(M9&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 4</t>
+        </is>
+      </c>
+      <c r="B10" s="241" t="n"/>
+      <c r="C10" s="258" t="n"/>
+      <c r="D10" s="258" t="n"/>
+      <c r="E10" s="258" t="n"/>
+      <c r="F10" s="258" t="n"/>
+      <c r="G10" s="258" t="n"/>
+      <c r="H10" s="258" t="n"/>
+      <c r="I10" s="258" t="n"/>
+      <c r="J10" s="258" t="n"/>
+      <c r="K10" s="258" t="n"/>
+      <c r="L10" s="258" t="n"/>
+      <c r="M10" s="259">
+        <f>IFERROR(AVERAGE(C10:L10),"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="241">
+        <f>IF(M10="","",IF(M10&gt;$B$3,"Superior",IF(M10&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 5</t>
+        </is>
+      </c>
+      <c r="B11" s="241" t="n"/>
+      <c r="C11" s="258" t="n"/>
+      <c r="D11" s="258" t="n"/>
+      <c r="E11" s="258" t="n"/>
+      <c r="F11" s="258" t="n"/>
+      <c r="G11" s="258" t="n"/>
+      <c r="H11" s="258" t="n"/>
+      <c r="I11" s="258" t="n"/>
+      <c r="J11" s="258" t="n"/>
+      <c r="K11" s="258" t="n"/>
+      <c r="L11" s="258" t="n"/>
+      <c r="M11" s="259">
+        <f>IFERROR(AVERAGE(C11:L11),"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="241">
+        <f>IF(M11="","",IF(M11&gt;$B$3,"Superior",IF(M11&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 6</t>
+        </is>
+      </c>
+      <c r="B12" s="241" t="n"/>
+      <c r="C12" s="258" t="n"/>
+      <c r="D12" s="258" t="n"/>
+      <c r="E12" s="258" t="n"/>
+      <c r="F12" s="258" t="n"/>
+      <c r="G12" s="258" t="n"/>
+      <c r="H12" s="258" t="n"/>
+      <c r="I12" s="258" t="n"/>
+      <c r="J12" s="258" t="n"/>
+      <c r="K12" s="258" t="n"/>
+      <c r="L12" s="258" t="n"/>
+      <c r="M12" s="259">
+        <f>IFERROR(AVERAGE(C12:L12),"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="241">
+        <f>IF(M12="","",IF(M12&gt;$B$3,"Superior",IF(M12&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 7</t>
+        </is>
+      </c>
+      <c r="B13" s="241" t="n"/>
+      <c r="C13" s="258" t="n"/>
+      <c r="D13" s="258" t="n"/>
+      <c r="E13" s="258" t="n"/>
+      <c r="F13" s="258" t="n"/>
+      <c r="G13" s="258" t="n"/>
+      <c r="H13" s="258" t="n"/>
+      <c r="I13" s="258" t="n"/>
+      <c r="J13" s="258" t="n"/>
+      <c r="K13" s="258" t="n"/>
+      <c r="L13" s="258" t="n"/>
+      <c r="M13" s="259">
+        <f>IFERROR(AVERAGE(C13:L13),"")</f>
+        <v/>
+      </c>
+      <c r="N13" s="241">
+        <f>IF(M13="","",IF(M13&gt;$B$3,"Superior",IF(M13&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 8</t>
+        </is>
+      </c>
+      <c r="B14" s="241" t="n"/>
+      <c r="C14" s="258" t="n"/>
+      <c r="D14" s="258" t="n"/>
+      <c r="E14" s="258" t="n"/>
+      <c r="F14" s="258" t="n"/>
+      <c r="G14" s="258" t="n"/>
+      <c r="H14" s="258" t="n"/>
+      <c r="I14" s="258" t="n"/>
+      <c r="J14" s="258" t="n"/>
+      <c r="K14" s="258" t="n"/>
+      <c r="L14" s="258" t="n"/>
+      <c r="M14" s="259">
+        <f>IFERROR(AVERAGE(C14:L14),"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="241">
+        <f>IF(M14="","",IF(M14&gt;$B$3,"Superior",IF(M14&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 9</t>
+        </is>
+      </c>
+      <c r="B15" s="241" t="n"/>
+      <c r="C15" s="258" t="n"/>
+      <c r="D15" s="258" t="n"/>
+      <c r="E15" s="258" t="n"/>
+      <c r="F15" s="258" t="n"/>
+      <c r="G15" s="258" t="n"/>
+      <c r="H15" s="258" t="n"/>
+      <c r="I15" s="258" t="n"/>
+      <c r="J15" s="258" t="n"/>
+      <c r="K15" s="258" t="n"/>
+      <c r="L15" s="258" t="n"/>
+      <c r="M15" s="259">
+        <f>IFERROR(AVERAGE(C15:L15),"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="241">
+        <f>IF(M15="","",IF(M15&gt;$B$3,"Superior",IF(M15&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 10</t>
+        </is>
+      </c>
+      <c r="B16" s="241" t="n"/>
+      <c r="C16" s="258" t="n"/>
+      <c r="D16" s="258" t="n"/>
+      <c r="E16" s="258" t="n"/>
+      <c r="F16" s="258" t="n"/>
+      <c r="G16" s="258" t="n"/>
+      <c r="H16" s="258" t="n"/>
+      <c r="I16" s="258" t="n"/>
+      <c r="J16" s="258" t="n"/>
+      <c r="K16" s="258" t="n"/>
+      <c r="L16" s="258" t="n"/>
+      <c r="M16" s="259">
+        <f>IFERROR(AVERAGE(C16:L16),"")</f>
+        <v/>
+      </c>
+      <c r="N16" s="241">
+        <f>IF(M16="","",IF(M16&gt;$B$3,"Superior",IF(M16&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t># Superior:</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>COUNTIF(N7:N16,"Superior")</f>
+        <v/>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t># Similar:</t>
+        </is>
+      </c>
+      <c r="D18">
+        <f>COUNTIF(N7:N16,"Similar")</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t># Inferior:</t>
+        </is>
+      </c>
+      <c r="F18">
+        <f>COUNTIF(N7:N16,"Inferior")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Green cells = manual entry (0 / 1 / -1 per factor; 1 = comp superior to subject, -1 = comp inferior to subject, 0 = similar). Overall and Rating are computed. Qualitative scores are descriptive only and do not affect the value indication.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="160" min="1" max="1"/>
+    <col width="20" customWidth="1" style="160" min="2" max="2"/>
+    <col width="12" customWidth="1" style="160" min="3" max="3"/>
+    <col width="12" customWidth="1" style="160" min="4" max="4"/>
+    <col width="12" customWidth="1" style="160" min="5" max="5"/>
+    <col width="12" customWidth="1" style="160" min="6" max="6"/>
+    <col width="12" customWidth="1" style="160" min="7" max="7"/>
+    <col width="12" customWidth="1" style="160" min="8" max="8"/>
+    <col width="10" customWidth="1" style="160" min="9" max="9"/>
+    <col width="11" customWidth="1" style="160" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Qualitative Analysis Grid — Land Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Threshold (|Overall| below this = Similar):</t>
+        </is>
+      </c>
+      <c r="B3" s="241" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>← Retune Superior/Similar/Inferior sensitivity here, per assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="242" t="inlineStr">
+        <is>
+          <t>Comp</t>
+        </is>
+      </c>
+      <c r="B6" s="242" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C6" s="242" t="inlineStr">
+        <is>
+          <t>Topography</t>
+        </is>
+      </c>
+      <c r="D6" s="242" t="inlineStr">
+        <is>
+          <t>Surrounding Land Uses</t>
+        </is>
+      </c>
+      <c r="E6" s="242" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="F6" s="242" t="inlineStr">
+        <is>
+          <t>Visibility</t>
+        </is>
+      </c>
+      <c r="G6" s="242" t="inlineStr">
+        <is>
+          <t>Flood Zone</t>
+        </is>
+      </c>
+      <c r="H6" s="242" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="I6" s="242" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="J6" s="242" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 1</t>
+        </is>
+      </c>
+      <c r="B7" s="241" t="n"/>
+      <c r="C7" s="258" t="n"/>
+      <c r="D7" s="258" t="n"/>
+      <c r="E7" s="258" t="n"/>
+      <c r="F7" s="258" t="n"/>
+      <c r="G7" s="258" t="n"/>
+      <c r="H7" s="258" t="n"/>
+      <c r="I7" s="259">
+        <f>IFERROR(AVERAGE(C7:H7),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="241">
+        <f>IF(I7="","",IF(I7&gt;$B$3,"Superior",IF(I7&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 2</t>
+        </is>
+      </c>
+      <c r="B8" s="241" t="n"/>
+      <c r="C8" s="258" t="n"/>
+      <c r="D8" s="258" t="n"/>
+      <c r="E8" s="258" t="n"/>
+      <c r="F8" s="258" t="n"/>
+      <c r="G8" s="258" t="n"/>
+      <c r="H8" s="258" t="n"/>
+      <c r="I8" s="259">
+        <f>IFERROR(AVERAGE(C8:H8),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="241">
+        <f>IF(I8="","",IF(I8&gt;$B$3,"Superior",IF(I8&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 3</t>
+        </is>
+      </c>
+      <c r="B9" s="241" t="n"/>
+      <c r="C9" s="258" t="n"/>
+      <c r="D9" s="258" t="n"/>
+      <c r="E9" s="258" t="n"/>
+      <c r="F9" s="258" t="n"/>
+      <c r="G9" s="258" t="n"/>
+      <c r="H9" s="258" t="n"/>
+      <c r="I9" s="259">
+        <f>IFERROR(AVERAGE(C9:H9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="241">
+        <f>IF(I9="","",IF(I9&gt;$B$3,"Superior",IF(I9&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 4</t>
+        </is>
+      </c>
+      <c r="B10" s="241" t="n"/>
+      <c r="C10" s="258" t="n"/>
+      <c r="D10" s="258" t="n"/>
+      <c r="E10" s="258" t="n"/>
+      <c r="F10" s="258" t="n"/>
+      <c r="G10" s="258" t="n"/>
+      <c r="H10" s="258" t="n"/>
+      <c r="I10" s="259">
+        <f>IFERROR(AVERAGE(C10:H10),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="241">
+        <f>IF(I10="","",IF(I10&gt;$B$3,"Superior",IF(I10&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 5</t>
+        </is>
+      </c>
+      <c r="B11" s="241" t="n"/>
+      <c r="C11" s="258" t="n"/>
+      <c r="D11" s="258" t="n"/>
+      <c r="E11" s="258" t="n"/>
+      <c r="F11" s="258" t="n"/>
+      <c r="G11" s="258" t="n"/>
+      <c r="H11" s="258" t="n"/>
+      <c r="I11" s="259">
+        <f>IFERROR(AVERAGE(C11:H11),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="241">
+        <f>IF(I11="","",IF(I11&gt;$B$3,"Superior",IF(I11&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 6</t>
+        </is>
+      </c>
+      <c r="B12" s="241" t="n"/>
+      <c r="C12" s="258" t="n"/>
+      <c r="D12" s="258" t="n"/>
+      <c r="E12" s="258" t="n"/>
+      <c r="F12" s="258" t="n"/>
+      <c r="G12" s="258" t="n"/>
+      <c r="H12" s="258" t="n"/>
+      <c r="I12" s="259">
+        <f>IFERROR(AVERAGE(C12:H12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="241">
+        <f>IF(I12="","",IF(I12&gt;$B$3,"Superior",IF(I12&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 7</t>
+        </is>
+      </c>
+      <c r="B13" s="241" t="n"/>
+      <c r="C13" s="258" t="n"/>
+      <c r="D13" s="258" t="n"/>
+      <c r="E13" s="258" t="n"/>
+      <c r="F13" s="258" t="n"/>
+      <c r="G13" s="258" t="n"/>
+      <c r="H13" s="258" t="n"/>
+      <c r="I13" s="259">
+        <f>IFERROR(AVERAGE(C13:H13),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="241">
+        <f>IF(I13="","",IF(I13&gt;$B$3,"Superior",IF(I13&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 8</t>
+        </is>
+      </c>
+      <c r="B14" s="241" t="n"/>
+      <c r="C14" s="258" t="n"/>
+      <c r="D14" s="258" t="n"/>
+      <c r="E14" s="258" t="n"/>
+      <c r="F14" s="258" t="n"/>
+      <c r="G14" s="258" t="n"/>
+      <c r="H14" s="258" t="n"/>
+      <c r="I14" s="259">
+        <f>IFERROR(AVERAGE(C14:H14),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="241">
+        <f>IF(I14="","",IF(I14&gt;$B$3,"Superior",IF(I14&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 9</t>
+        </is>
+      </c>
+      <c r="B15" s="241" t="n"/>
+      <c r="C15" s="258" t="n"/>
+      <c r="D15" s="258" t="n"/>
+      <c r="E15" s="258" t="n"/>
+      <c r="F15" s="258" t="n"/>
+      <c r="G15" s="258" t="n"/>
+      <c r="H15" s="258" t="n"/>
+      <c r="I15" s="259">
+        <f>IFERROR(AVERAGE(C15:H15),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="241">
+        <f>IF(I15="","",IF(I15&gt;$B$3,"Superior",IF(I15&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="243" t="inlineStr">
+        <is>
+          <t>Sale No. 10</t>
+        </is>
+      </c>
+      <c r="B16" s="241" t="n"/>
+      <c r="C16" s="258" t="n"/>
+      <c r="D16" s="258" t="n"/>
+      <c r="E16" s="258" t="n"/>
+      <c r="F16" s="258" t="n"/>
+      <c r="G16" s="258" t="n"/>
+      <c r="H16" s="258" t="n"/>
+      <c r="I16" s="259">
+        <f>IFERROR(AVERAGE(C16:H16),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="241">
+        <f>IF(I16="","",IF(I16&gt;$B$3,"Superior",IF(I16&lt;-$B$3,"Inferior","Similar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t># Superior:</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>COUNTIF(J7:J16,"Superior")</f>
+        <v/>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t># Similar:</t>
+        </is>
+      </c>
+      <c r="D18">
+        <f>COUNTIF(J7:J16,"Similar")</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t># Inferior:</t>
+        </is>
+      </c>
+      <c r="F18">
+        <f>COUNTIF(J7:J16,"Inferior")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Green cells = manual entry (0 / 1 / -1 per factor; 1 = comp superior to subject, -1 = comp inferior to subject, 0 = similar). Overall and Rating are computed. Qualitative scores are descriptive only and do not affect the value indication.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
